--- a/documentation/pinout.xlsx
+++ b/documentation/pinout.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hobby\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hobby\share\allwinner_d1_hal\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -755,6 +755,7 @@
     <col min="4" max="4" width="10.04296875" customWidth="1"/>
     <col min="7" max="7" width="8.26953125" customWidth="1"/>
     <col min="8" max="8" width="11.26953125" customWidth="1"/>
+    <col min="11" max="11" width="13.58984375" customWidth="1"/>
     <col min="14" max="14" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/documentation/pinout.xlsx
+++ b/documentation/pinout.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7060"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="140">
   <si>
     <t>Pin</t>
   </si>
@@ -381,6 +381,69 @@
   </si>
   <si>
     <t>11c</t>
+  </si>
+  <si>
+    <t>TXW686013B0</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>PCLK</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>VS</t>
+  </si>
+  <si>
+    <t>DEN</t>
   </si>
 </sst>
 </file>
@@ -418,7 +481,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +500,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -450,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -468,6 +543,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -749,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
   <cols>
     <col min="4" max="4" width="10.04296875" customWidth="1"/>
@@ -1534,1039 +1617,1897 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.65">
-      <c r="A44" s="1"/>
-      <c r="H44" s="8"/>
+      <c r="C44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H44" s="12"/>
+      <c r="K44" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.65">
-      <c r="A45" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H45" s="8"/>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="13">
+        <v>28</v>
+      </c>
+      <c r="K45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="8"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.65">
-      <c r="A46" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="C46" s="1">
+        <v>2</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" t="s">
+        <v>83</v>
+      </c>
+      <c r="F46" t="s">
+        <v>107</v>
+      </c>
+      <c r="H46" s="13">
+        <v>35</v>
+      </c>
+      <c r="J46" s="8"/>
+      <c r="K46" t="s">
+        <v>2</v>
+      </c>
+      <c r="L46" s="1">
+        <v>2</v>
+      </c>
+      <c r="M46" s="8"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C47" s="1">
+        <v>3</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" t="s">
+        <v>107</v>
+      </c>
+      <c r="H47" s="13">
+        <v>37</v>
+      </c>
+      <c r="J47" s="8"/>
+      <c r="K47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="1">
+        <v>3</v>
+      </c>
+      <c r="M47" s="8"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C48" s="1">
+        <v>4</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="13">
+        <v>38</v>
+      </c>
+      <c r="J48" s="8"/>
+      <c r="K48" t="s">
+        <v>76</v>
+      </c>
+      <c r="L48" s="1">
+        <v>4</v>
+      </c>
+      <c r="M48" s="8"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C49" s="1">
+        <v>5</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49" t="s">
+        <v>109</v>
+      </c>
+      <c r="H49" s="13"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L49" s="1">
+        <v>5</v>
+      </c>
+      <c r="M49" s="8"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C50" s="1">
+        <v>6</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H50" s="13"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L50" s="1">
+        <v>6</v>
+      </c>
+      <c r="M50" s="8"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C51" s="1">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H51" s="13"/>
+      <c r="J51" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L51" s="1">
+        <v>7</v>
+      </c>
+      <c r="M51" s="8"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C52" s="1">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" t="s">
+        <v>81</v>
+      </c>
+      <c r="F52" t="s">
+        <v>110</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="J52" t="s">
+        <v>53</v>
+      </c>
+      <c r="K52" t="s">
+        <v>120</v>
+      </c>
+      <c r="L52" s="1">
+        <v>8</v>
+      </c>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C53" s="1">
+        <v>9</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" t="s">
+        <v>95</v>
+      </c>
+      <c r="F53" t="s">
+        <v>110</v>
+      </c>
+      <c r="H53" s="13"/>
+      <c r="J53" t="s">
+        <v>56</v>
+      </c>
+      <c r="K53" t="s">
+        <v>121</v>
+      </c>
+      <c r="L53" s="1">
+        <v>9</v>
+      </c>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C54" s="1">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="13"/>
+      <c r="J54" t="s">
+        <v>58</v>
+      </c>
+      <c r="K54" t="s">
+        <v>122</v>
+      </c>
+      <c r="L54" s="1">
+        <v>10</v>
+      </c>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C55" s="1">
+        <v>11</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" t="s">
+        <v>80</v>
+      </c>
+      <c r="F55" t="s">
+        <v>108</v>
+      </c>
+      <c r="H55" s="13"/>
+      <c r="J55" t="s">
+        <v>89</v>
+      </c>
+      <c r="K55" t="s">
+        <v>123</v>
+      </c>
+      <c r="L55" s="1">
+        <v>11</v>
+      </c>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C56" s="1">
+        <v>12</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F56" t="s">
+        <v>108</v>
+      </c>
+      <c r="H56" s="13"/>
+      <c r="J56" t="s">
+        <v>75</v>
+      </c>
+      <c r="K56" t="s">
+        <v>124</v>
+      </c>
+      <c r="L56" s="1">
+        <v>12</v>
+      </c>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C57" s="1">
+        <v>13</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="13"/>
+      <c r="J57" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="1">
+        <v>13</v>
+      </c>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C58" s="1">
+        <v>14</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H58" s="13"/>
+      <c r="J58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="1">
+        <v>14</v>
+      </c>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C59" s="1">
+        <v>15</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" t="s">
+        <v>111</v>
+      </c>
+      <c r="H59" s="13">
+        <v>11</v>
+      </c>
+      <c r="J59" t="s">
+        <v>80</v>
+      </c>
+      <c r="K59" t="s">
+        <v>125</v>
+      </c>
+      <c r="L59" s="1">
+        <v>15</v>
+      </c>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C60" s="1">
+        <v>16</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="13">
+        <v>12</v>
+      </c>
+      <c r="J60" t="s">
+        <v>94</v>
+      </c>
+      <c r="K60" t="s">
+        <v>126</v>
+      </c>
+      <c r="L60" s="1">
+        <v>16</v>
+      </c>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C61" s="1">
+        <v>17</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H61" s="13">
+        <v>14</v>
+      </c>
+      <c r="J61" t="s">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s">
+        <v>127</v>
+      </c>
+      <c r="L61" s="1">
+        <v>17</v>
+      </c>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C62" s="1">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="13">
+        <v>15</v>
+      </c>
+      <c r="J62" t="s">
+        <v>93</v>
+      </c>
+      <c r="K62" t="s">
+        <v>128</v>
+      </c>
+      <c r="L62" s="1">
+        <v>18</v>
+      </c>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C63" s="1">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" s="13"/>
+      <c r="J63" t="s">
         <v>52</v>
       </c>
-      <c r="C46" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.65">
-      <c r="A47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="K63" t="s">
+        <v>129</v>
+      </c>
+      <c r="L63" s="1">
+        <v>19</v>
+      </c>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C64" s="1">
+        <v>20</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64" s="13"/>
+      <c r="J64" t="s">
         <v>49</v>
       </c>
-      <c r="C47" t="s">
-        <v>60</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E47" t="s">
-        <v>116</v>
-      </c>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.65">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" t="s">
-        <v>61</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" t="s">
-        <v>117</v>
-      </c>
-      <c r="H48" s="8"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A49" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" t="s">
-        <v>118</v>
-      </c>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="C52" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="D54" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="D55" s="9"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="D56" s="9"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A57" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="K57" s="6" t="s">
+      <c r="K64" t="s">
+        <v>130</v>
+      </c>
+      <c r="L64" s="1">
+        <v>20</v>
+      </c>
+      <c r="M64" s="8"/>
+    </row>
+    <row r="65" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C65" s="1">
+        <v>21</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H65" s="13"/>
+      <c r="J65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L65" s="1">
+        <v>21</v>
+      </c>
+      <c r="M65" s="8"/>
+    </row>
+    <row r="66" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C66" s="1">
+        <v>22</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="13"/>
+      <c r="J66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="1">
+        <v>22</v>
+      </c>
+      <c r="M66" s="8"/>
+    </row>
+    <row r="67" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C67" s="1">
+        <v>23</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H67" s="13">
+        <v>2</v>
+      </c>
+      <c r="J67" t="s">
+        <v>83</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L67" s="1">
+        <v>23</v>
+      </c>
+      <c r="M67" s="8"/>
+    </row>
+    <row r="68" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C68" s="1">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" s="13">
+        <v>3</v>
+      </c>
+      <c r="J68" t="s">
+        <v>97</v>
+      </c>
+      <c r="K68" t="s">
+        <v>131</v>
+      </c>
+      <c r="L68" s="1">
+        <v>24</v>
+      </c>
+      <c r="M68" s="8"/>
+    </row>
+    <row r="69" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C69" s="1">
+        <v>25</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H69" s="13">
+        <v>5</v>
+      </c>
+      <c r="J69" t="s">
+        <v>82</v>
+      </c>
+      <c r="K69" t="s">
+        <v>132</v>
+      </c>
+      <c r="L69" s="1">
+        <v>25</v>
+      </c>
+      <c r="M69" s="8"/>
+    </row>
+    <row r="70" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C70" s="1">
+        <v>26</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H70" s="13">
+        <v>6</v>
+      </c>
+      <c r="J70" t="s">
+        <v>96</v>
+      </c>
+      <c r="K70" t="s">
+        <v>133</v>
+      </c>
+      <c r="L70" s="1">
+        <v>26</v>
+      </c>
+      <c r="M70" s="8"/>
+    </row>
+    <row r="71" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C71" s="1">
+        <v>27</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H71" s="13">
+        <v>8</v>
+      </c>
+      <c r="J71" t="s">
+        <v>81</v>
+      </c>
+      <c r="K71" t="s">
+        <v>134</v>
+      </c>
+      <c r="L71" s="1">
+        <v>27</v>
+      </c>
+      <c r="M71" s="8"/>
+    </row>
+    <row r="72" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C72" s="1">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>44</v>
+      </c>
+      <c r="H72" s="13">
+        <v>9</v>
+      </c>
+      <c r="J72" t="s">
+        <v>95</v>
+      </c>
+      <c r="K72" t="s">
+        <v>135</v>
+      </c>
+      <c r="L72" s="1">
+        <v>28</v>
+      </c>
+      <c r="M72" s="8"/>
+    </row>
+    <row r="73" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C73" s="1">
+        <v>29</v>
+      </c>
+      <c r="D73" t="s">
+        <v>44</v>
+      </c>
+      <c r="H73" s="13">
         <v>33</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="D58" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="G58" s="7"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A59" t="s">
-        <v>76</v>
-      </c>
-      <c r="B59" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" t="s">
-        <v>2</v>
-      </c>
-      <c r="E59" s="1">
-        <v>2</v>
-      </c>
-      <c r="G59" s="7"/>
-      <c r="H59" t="s">
-        <v>76</v>
-      </c>
-      <c r="I59" s="1">
-        <v>4</v>
-      </c>
-      <c r="J59" s="1">
-        <v>2</v>
-      </c>
-      <c r="K59" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A60" t="s">
-        <v>71</v>
-      </c>
-      <c r="B60" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" s="1">
-        <v>3</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1">
-        <v>3</v>
-      </c>
-      <c r="K60" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A61" t="s">
-        <v>72</v>
-      </c>
-      <c r="B61" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" t="s">
-        <v>76</v>
-      </c>
-      <c r="E61" s="1">
-        <v>4</v>
-      </c>
-      <c r="G61" s="7"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1">
-        <v>4</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A62" t="s">
-        <v>73</v>
-      </c>
-      <c r="B62" t="s">
-        <v>86</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="1">
-        <v>5</v>
-      </c>
-      <c r="G62" s="7"/>
-      <c r="H62" t="s">
+      <c r="J73" s="8"/>
+      <c r="K73" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L73" s="1">
+        <v>29</v>
+      </c>
+      <c r="M73" s="8"/>
+    </row>
+    <row r="74" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C74" s="1">
+        <v>30</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H74" s="13"/>
+      <c r="J74" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K74" t="s">
+        <v>136</v>
+      </c>
+      <c r="L74" s="1">
+        <v>30</v>
+      </c>
+      <c r="M74" s="8"/>
+    </row>
+    <row r="75" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C75" s="1">
+        <v>31</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="13"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L75" s="1">
+        <v>31</v>
+      </c>
+      <c r="M75" s="8"/>
+    </row>
+    <row r="76" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C76" s="1">
+        <v>32</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="13"/>
+      <c r="J76" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K76" t="s">
+        <v>137</v>
+      </c>
+      <c r="L76" s="1">
+        <v>32</v>
+      </c>
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C77" s="1">
+        <v>33</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1"/>
+      <c r="H77" s="13"/>
+      <c r="J77" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="K77" t="s">
+        <v>138</v>
+      </c>
+      <c r="L77" s="1">
+        <v>33</v>
+      </c>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C78" s="1">
+        <v>34</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="13"/>
+      <c r="J78" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s">
+        <v>139</v>
+      </c>
+      <c r="L78" s="1">
+        <v>34</v>
+      </c>
+      <c r="M78" s="8"/>
+    </row>
+    <row r="79" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C79" s="1">
+        <v>35</v>
+      </c>
+      <c r="D79" t="s">
+        <v>45</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="13"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L79" s="1">
+        <v>35</v>
+      </c>
+      <c r="M79" s="8"/>
+    </row>
+    <row r="80" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="C80" s="1">
+        <v>36</v>
+      </c>
+      <c r="D80" t="s">
+        <v>45</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="13">
+        <v>32</v>
+      </c>
+      <c r="J80" s="8"/>
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="1">
+        <v>36</v>
+      </c>
+      <c r="M80" s="8"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C81" s="1">
+        <v>37</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="13"/>
+      <c r="J81" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="I62" s="1">
-        <v>37</v>
-      </c>
-      <c r="J62" s="1">
-        <v>5</v>
-      </c>
-      <c r="K62" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" t="s">
-        <v>87</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E63" s="1">
-        <v>6</v>
-      </c>
-      <c r="G63" s="7"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1">
-        <v>6</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A64" t="s">
-        <v>74</v>
-      </c>
-      <c r="B64" t="s">
-        <v>88</v>
-      </c>
-      <c r="D64" t="s">
-        <v>50</v>
-      </c>
-      <c r="E64" s="1">
-        <v>7</v>
-      </c>
-      <c r="G64" s="7"/>
-      <c r="H64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I64" s="1">
-        <v>3</v>
-      </c>
-      <c r="J64" s="1">
-        <v>7</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A65" t="s">
-        <v>75</v>
-      </c>
-      <c r="B65" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" t="s">
-        <v>53</v>
-      </c>
-      <c r="E65" s="1">
-        <v>8</v>
-      </c>
-      <c r="G65" s="7"/>
-      <c r="H65" t="s">
-        <v>97</v>
-      </c>
-      <c r="I65" s="1">
-        <v>24</v>
-      </c>
-      <c r="J65" s="1">
-        <v>8</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66" t="s">
-        <v>56</v>
-      </c>
-      <c r="E66" s="1">
-        <v>9</v>
-      </c>
-      <c r="G66" s="7"/>
-      <c r="H66" t="s">
-        <v>83</v>
-      </c>
-      <c r="I66" s="1">
-        <v>23</v>
-      </c>
-      <c r="J66" s="1">
-        <v>9</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A67" t="s">
-        <v>53</v>
-      </c>
-      <c r="B67" t="s">
-        <v>90</v>
-      </c>
-      <c r="D67" t="s">
-        <v>58</v>
-      </c>
-      <c r="E67" s="1">
-        <v>10</v>
-      </c>
-      <c r="G67" s="7"/>
-      <c r="H67" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I67" s="1">
-        <v>6</v>
-      </c>
-      <c r="J67" s="1">
-        <v>10</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A68" t="s">
-        <v>50</v>
-      </c>
-      <c r="B68" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" t="s">
-        <v>89</v>
-      </c>
-      <c r="E68" s="1">
-        <v>11</v>
-      </c>
-      <c r="G68" s="7"/>
-      <c r="H68" t="s">
-        <v>96</v>
-      </c>
-      <c r="I68" s="1">
-        <v>26</v>
-      </c>
-      <c r="J68" s="1">
-        <v>11</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A69" t="s">
-        <v>52</v>
-      </c>
-      <c r="B69" t="s">
-        <v>49</v>
-      </c>
-      <c r="D69" t="s">
-        <v>75</v>
-      </c>
-      <c r="E69" s="1">
-        <v>12</v>
-      </c>
-      <c r="G69" s="7"/>
-      <c r="H69" t="s">
-        <v>82</v>
-      </c>
-      <c r="I69" s="1">
-        <v>25</v>
-      </c>
-      <c r="J69" s="1">
-        <v>12</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A70" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" t="s">
-        <v>91</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E70" s="1">
-        <v>13</v>
-      </c>
-      <c r="G70" s="7"/>
-      <c r="H70" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I70" s="1">
-        <v>13</v>
-      </c>
-      <c r="J70" s="1">
-        <v>13</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A71" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" t="s">
-        <v>92</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E71" s="1">
-        <v>14</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" t="s">
-        <v>95</v>
-      </c>
-      <c r="I71" s="1">
-        <v>28</v>
-      </c>
-      <c r="J71" s="1">
-        <v>14</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A72" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" t="s">
-        <v>93</v>
-      </c>
-      <c r="D72" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="1">
-        <v>15</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" t="s">
-        <v>81</v>
-      </c>
-      <c r="I72" s="1">
-        <v>27</v>
-      </c>
-      <c r="J72" s="1">
-        <v>15</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A73" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" t="s">
-        <v>94</v>
-      </c>
-      <c r="D73" t="s">
-        <v>94</v>
-      </c>
-      <c r="E73" s="1">
-        <v>16</v>
-      </c>
-      <c r="G73" s="7"/>
-      <c r="H73" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I73" s="1">
-        <v>14</v>
-      </c>
-      <c r="J73" s="1">
-        <v>16</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A74" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" t="s">
-        <v>95</v>
-      </c>
-      <c r="D74" t="s">
-        <v>79</v>
-      </c>
-      <c r="E74" s="1">
-        <v>17</v>
-      </c>
-      <c r="G74" s="7"/>
-      <c r="H74" t="s">
-        <v>94</v>
-      </c>
-      <c r="I74" s="1">
-        <v>16</v>
-      </c>
-      <c r="J74" s="1">
-        <v>17</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A75" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75" t="s">
-        <v>96</v>
-      </c>
-      <c r="D75" t="s">
-        <v>93</v>
-      </c>
-      <c r="E75" s="1">
-        <v>18</v>
-      </c>
-      <c r="G75" s="7"/>
-      <c r="H75" t="s">
-        <v>80</v>
-      </c>
-      <c r="I75" s="1">
-        <v>15</v>
-      </c>
-      <c r="J75" s="1">
-        <v>18</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A76" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" t="s">
-        <v>97</v>
-      </c>
-      <c r="D76" t="s">
-        <v>52</v>
-      </c>
-      <c r="E76" s="1">
-        <v>19</v>
-      </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="1">
-        <v>21</v>
-      </c>
-      <c r="J76" s="1">
-        <v>19</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B77" t="s">
-        <v>98</v>
-      </c>
-      <c r="D77" t="s">
-        <v>49</v>
-      </c>
-      <c r="E77" s="1">
-        <v>20</v>
-      </c>
-      <c r="G77" s="7"/>
-      <c r="H77" t="s">
-        <v>93</v>
-      </c>
-      <c r="I77" s="1">
-        <v>18</v>
-      </c>
-      <c r="J77" s="1">
-        <v>20</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="A78" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" t="s">
-        <v>99</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E78" s="1">
-        <v>21</v>
-      </c>
-      <c r="G78" s="7"/>
-      <c r="H78" t="s">
-        <v>79</v>
-      </c>
-      <c r="I78" s="1">
-        <v>17</v>
-      </c>
-      <c r="J78" s="1">
-        <v>21</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="D79" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E79" s="1">
-        <v>22</v>
-      </c>
-      <c r="G79" s="7"/>
-      <c r="H79" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I79" s="1">
-        <v>22</v>
-      </c>
-      <c r="J79" s="1">
-        <v>22</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="D80" t="s">
-        <v>83</v>
-      </c>
-      <c r="E80" s="1">
-        <v>23</v>
-      </c>
-      <c r="G80" s="7"/>
-      <c r="H80" t="s">
-        <v>52</v>
-      </c>
-      <c r="I80" s="1">
-        <v>19</v>
-      </c>
-      <c r="J80" s="1">
-        <v>23</v>
-      </c>
-      <c r="K80" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D81" t="s">
-        <v>97</v>
-      </c>
-      <c r="E81" s="1">
-        <v>24</v>
-      </c>
-      <c r="G81" s="7"/>
-      <c r="H81" t="s">
-        <v>49</v>
-      </c>
-      <c r="I81" s="1">
-        <v>20</v>
-      </c>
-      <c r="J81" s="1">
-        <v>24</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="L81" s="1">
+        <v>37</v>
+      </c>
+      <c r="M81" s="8"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C82" s="1">
+        <v>38</v>
+      </c>
       <c r="D82" t="s">
+        <v>104</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="13"/>
+      <c r="J82" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="K82" t="s">
+        <v>21</v>
+      </c>
+      <c r="L82" s="1">
+        <v>38</v>
+      </c>
+      <c r="M82" s="8"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C83" s="1">
+        <v>39</v>
+      </c>
+      <c r="D83" t="s">
+        <v>104</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="13">
+        <v>24</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K83" t="s">
+        <v>32</v>
+      </c>
+      <c r="L83" s="1">
+        <v>39</v>
+      </c>
+      <c r="M83" s="8"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C84" s="1">
+        <v>40</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="13"/>
+      <c r="J84" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K84" t="s">
+        <v>6</v>
+      </c>
+      <c r="L84" s="1">
+        <v>40</v>
+      </c>
+      <c r="M84" s="8"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A85" s="1"/>
+      <c r="H85" s="13"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A86" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H86" s="13"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A87" t="s">
+        <v>51</v>
+      </c>
+      <c r="B87" t="s">
+        <v>52</v>
+      </c>
+      <c r="C87" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H87" s="13"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A88" t="s">
+        <v>47</v>
+      </c>
+      <c r="B88" t="s">
+        <v>49</v>
+      </c>
+      <c r="C88" t="s">
+        <v>60</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E88" t="s">
+        <v>116</v>
+      </c>
+      <c r="H88" s="8"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A89" t="s">
+        <v>48</v>
+      </c>
+      <c r="B89" t="s">
+        <v>50</v>
+      </c>
+      <c r="C89" t="s">
+        <v>61</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E89" t="s">
+        <v>117</v>
+      </c>
+      <c r="H89" s="8"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A90" t="s">
+        <v>54</v>
+      </c>
+      <c r="B90" t="s">
+        <v>53</v>
+      </c>
+      <c r="C90" t="s">
+        <v>62</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" t="s">
+        <v>118</v>
+      </c>
+      <c r="H90" s="8"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A91" t="s">
+        <v>55</v>
+      </c>
+      <c r="B91" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" t="s">
+        <v>63</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="A92" t="s">
+        <v>57</v>
+      </c>
+      <c r="B92" t="s">
+        <v>58</v>
+      </c>
+      <c r="C92" t="s">
+        <v>64</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C93" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="C94" t="s">
+        <v>115</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="D95" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="D96" s="9"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D97" s="9"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A98" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D99" t="s">
+        <v>1</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="G99" s="7"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1">
+        <v>1</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A100" t="s">
+        <v>76</v>
+      </c>
+      <c r="B100" t="s">
+        <v>85</v>
+      </c>
+      <c r="D100" t="s">
+        <v>2</v>
+      </c>
+      <c r="E100" s="1">
+        <v>2</v>
+      </c>
+      <c r="G100" s="7"/>
+      <c r="H100" t="s">
+        <v>76</v>
+      </c>
+      <c r="I100" s="1">
+        <v>4</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2</v>
+      </c>
+      <c r="K100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A101" t="s">
+        <v>71</v>
+      </c>
+      <c r="B101" t="s">
+        <v>85</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="1">
+        <v>3</v>
+      </c>
+      <c r="G101" s="7"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1">
+        <v>3</v>
+      </c>
+      <c r="K101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A102" t="s">
+        <v>72</v>
+      </c>
+      <c r="B102" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" t="s">
+        <v>76</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4</v>
+      </c>
+      <c r="G102" s="7"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1">
+        <v>4</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A103" t="s">
+        <v>73</v>
+      </c>
+      <c r="B103" t="s">
+        <v>86</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E103" s="1">
+        <v>5</v>
+      </c>
+      <c r="G103" s="7"/>
+      <c r="H103" t="s">
+        <v>74</v>
+      </c>
+      <c r="I103" s="1">
+        <v>37</v>
+      </c>
+      <c r="J103" s="1">
+        <v>5</v>
+      </c>
+      <c r="K103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A104" t="s">
+        <v>56</v>
+      </c>
+      <c r="B104" t="s">
+        <v>87</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E104" s="1">
+        <v>6</v>
+      </c>
+      <c r="G104" s="7"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1">
+        <v>6</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A105" t="s">
+        <v>74</v>
+      </c>
+      <c r="B105" t="s">
+        <v>88</v>
+      </c>
+      <c r="D105" t="s">
+        <v>50</v>
+      </c>
+      <c r="E105" s="1">
+        <v>7</v>
+      </c>
+      <c r="G105" s="7"/>
+      <c r="H105" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I105" s="1">
+        <v>3</v>
+      </c>
+      <c r="J105" s="1">
+        <v>7</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A106" t="s">
+        <v>75</v>
+      </c>
+      <c r="B106" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" t="s">
+        <v>53</v>
+      </c>
+      <c r="E106" s="1">
+        <v>8</v>
+      </c>
+      <c r="G106" s="7"/>
+      <c r="H106" t="s">
+        <v>97</v>
+      </c>
+      <c r="I106" s="1">
+        <v>24</v>
+      </c>
+      <c r="J106" s="1">
+        <v>8</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A107" t="s">
+        <v>58</v>
+      </c>
+      <c r="B107" t="s">
+        <v>89</v>
+      </c>
+      <c r="D107" t="s">
+        <v>56</v>
+      </c>
+      <c r="E107" s="1">
+        <v>9</v>
+      </c>
+      <c r="G107" s="7"/>
+      <c r="H107" t="s">
+        <v>83</v>
+      </c>
+      <c r="I107" s="1">
+        <v>23</v>
+      </c>
+      <c r="J107" s="1">
+        <v>9</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A108" t="s">
+        <v>53</v>
+      </c>
+      <c r="B108" t="s">
+        <v>90</v>
+      </c>
+      <c r="D108" t="s">
+        <v>58</v>
+      </c>
+      <c r="E108" s="1">
+        <v>10</v>
+      </c>
+      <c r="G108" s="7"/>
+      <c r="H108" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I108" s="1">
+        <v>6</v>
+      </c>
+      <c r="J108" s="1">
+        <v>10</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A109" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" t="s">
+        <v>89</v>
+      </c>
+      <c r="E109" s="1">
+        <v>11</v>
+      </c>
+      <c r="G109" s="7"/>
+      <c r="H109" t="s">
+        <v>96</v>
+      </c>
+      <c r="I109" s="1">
+        <v>26</v>
+      </c>
+      <c r="J109" s="1">
+        <v>11</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A110" t="s">
+        <v>52</v>
+      </c>
+      <c r="B110" t="s">
+        <v>49</v>
+      </c>
+      <c r="D110" t="s">
+        <v>75</v>
+      </c>
+      <c r="E110" s="1">
+        <v>12</v>
+      </c>
+      <c r="G110" s="7"/>
+      <c r="H110" t="s">
         <v>82</v>
       </c>
-      <c r="E82" s="1">
+      <c r="I110" s="1">
         <v>25</v>
       </c>
-      <c r="G82" s="7"/>
-      <c r="H82" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I82" s="1">
+      <c r="J110" s="1">
+        <v>12</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A111" t="s">
+        <v>77</v>
+      </c>
+      <c r="B111" t="s">
+        <v>91</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E111" s="1">
+        <v>13</v>
+      </c>
+      <c r="G111" s="7"/>
+      <c r="H111" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I111" s="1">
+        <v>13</v>
+      </c>
+      <c r="J111" s="1">
+        <v>13</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A112" t="s">
+        <v>78</v>
+      </c>
+      <c r="B112" t="s">
+        <v>92</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E112" s="1">
+        <v>14</v>
+      </c>
+      <c r="G112" s="7"/>
+      <c r="H112" t="s">
+        <v>95</v>
+      </c>
+      <c r="I112" s="1">
+        <v>28</v>
+      </c>
+      <c r="J112" s="1">
+        <v>14</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A113" t="s">
+        <v>79</v>
+      </c>
+      <c r="B113" t="s">
+        <v>93</v>
+      </c>
+      <c r="D113" t="s">
+        <v>80</v>
+      </c>
+      <c r="E113" s="1">
+        <v>15</v>
+      </c>
+      <c r="G113" s="7"/>
+      <c r="H113" t="s">
+        <v>81</v>
+      </c>
+      <c r="I113" s="1">
+        <v>27</v>
+      </c>
+      <c r="J113" s="1">
+        <v>15</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A114" t="s">
+        <v>80</v>
+      </c>
+      <c r="B114" t="s">
+        <v>94</v>
+      </c>
+      <c r="D114" t="s">
+        <v>94</v>
+      </c>
+      <c r="E114" s="1">
+        <v>16</v>
+      </c>
+      <c r="G114" s="7"/>
+      <c r="H114" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I114" s="1">
+        <v>14</v>
+      </c>
+      <c r="J114" s="1">
+        <v>16</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A115" t="s">
+        <v>81</v>
+      </c>
+      <c r="B115" t="s">
+        <v>95</v>
+      </c>
+      <c r="D115" t="s">
+        <v>79</v>
+      </c>
+      <c r="E115" s="1">
+        <v>17</v>
+      </c>
+      <c r="G115" s="7"/>
+      <c r="H115" t="s">
+        <v>94</v>
+      </c>
+      <c r="I115" s="1">
+        <v>16</v>
+      </c>
+      <c r="J115" s="1">
+        <v>17</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A116" t="s">
+        <v>82</v>
+      </c>
+      <c r="B116" t="s">
+        <v>96</v>
+      </c>
+      <c r="D116" t="s">
+        <v>93</v>
+      </c>
+      <c r="E116" s="1">
+        <v>18</v>
+      </c>
+      <c r="G116" s="7"/>
+      <c r="H116" t="s">
+        <v>80</v>
+      </c>
+      <c r="I116" s="1">
+        <v>15</v>
+      </c>
+      <c r="J116" s="1">
+        <v>18</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A117" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" t="s">
+        <v>97</v>
+      </c>
+      <c r="D117" t="s">
+        <v>52</v>
+      </c>
+      <c r="E117" s="1">
+        <v>19</v>
+      </c>
+      <c r="G117" s="7"/>
+      <c r="H117" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I117" s="1">
+        <v>21</v>
+      </c>
+      <c r="J117" s="1">
+        <v>19</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A118" t="s">
+        <v>84</v>
+      </c>
+      <c r="B118" t="s">
+        <v>98</v>
+      </c>
+      <c r="D118" t="s">
+        <v>49</v>
+      </c>
+      <c r="E118" s="1">
+        <v>20</v>
+      </c>
+      <c r="G118" s="7"/>
+      <c r="H118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I118" s="1">
+        <v>18</v>
+      </c>
+      <c r="J118" s="1">
+        <v>20</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="A119" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" t="s">
+        <v>99</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E119" s="1">
+        <v>21</v>
+      </c>
+      <c r="G119" s="7"/>
+      <c r="H119" t="s">
+        <v>79</v>
+      </c>
+      <c r="I119" s="1">
+        <v>17</v>
+      </c>
+      <c r="J119" s="1">
+        <v>21</v>
+      </c>
+      <c r="K119" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D120" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E120" s="1">
+        <v>22</v>
+      </c>
+      <c r="G120" s="7"/>
+      <c r="H120" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I120" s="1">
+        <v>22</v>
+      </c>
+      <c r="J120" s="1">
+        <v>22</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D121" t="s">
+        <v>83</v>
+      </c>
+      <c r="E121" s="1">
+        <v>23</v>
+      </c>
+      <c r="G121" s="7"/>
+      <c r="H121" t="s">
+        <v>52</v>
+      </c>
+      <c r="I121" s="1">
+        <v>19</v>
+      </c>
+      <c r="J121" s="1">
+        <v>23</v>
+      </c>
+      <c r="K121" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D122" t="s">
+        <v>97</v>
+      </c>
+      <c r="E122" s="1">
+        <v>24</v>
+      </c>
+      <c r="G122" s="7"/>
+      <c r="H122" t="s">
+        <v>49</v>
+      </c>
+      <c r="I122" s="1">
+        <v>20</v>
+      </c>
+      <c r="J122" s="1">
+        <v>24</v>
+      </c>
+      <c r="K122" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D123" t="s">
+        <v>82</v>
+      </c>
+      <c r="E123" s="1">
+        <v>25</v>
+      </c>
+      <c r="G123" s="7"/>
+      <c r="H123" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I123" s="1">
         <v>29</v>
       </c>
-      <c r="J82" s="1">
+      <c r="J123" s="1">
         <v>25</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D83" t="s">
+      <c r="K123" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D124" t="s">
         <v>96</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E124" s="1">
         <v>26</v>
       </c>
-      <c r="G83" s="7"/>
-      <c r="H83" t="s">
+      <c r="G124" s="7"/>
+      <c r="H124" t="s">
         <v>50</v>
       </c>
-      <c r="I83" s="1">
+      <c r="I124" s="1">
         <v>7</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J124" s="1">
         <v>26</v>
       </c>
-      <c r="K83" t="s">
+      <c r="K124" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D84" t="s">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D125" t="s">
         <v>81</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E125" s="1">
         <v>27</v>
       </c>
-      <c r="G84" s="7"/>
-      <c r="H84" t="s">
+      <c r="G125" s="7"/>
+      <c r="H125" t="s">
         <v>53</v>
       </c>
-      <c r="I84" s="1">
+      <c r="I125" s="1">
         <v>8</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J125" s="1">
         <v>27</v>
       </c>
-      <c r="K84" t="s">
+      <c r="K125" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D85" t="s">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D126" t="s">
         <v>95</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E126" s="1">
         <v>28</v>
       </c>
-      <c r="G85" s="7"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1">
+      <c r="G126" s="7"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1">
         <v>28</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="K126" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D86" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E86" s="1">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D127" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E127" s="1">
         <v>29</v>
       </c>
-      <c r="G86" s="7"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1">
+      <c r="G127" s="7"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1">
         <v>29</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="K127" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D87" t="s">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D128" t="s">
         <v>78</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E128" s="1">
         <v>30</v>
       </c>
-      <c r="G87" s="7"/>
-      <c r="H87" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I87" s="1">
+      <c r="G128" s="7"/>
+      <c r="H128" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I128" s="1">
         <v>36</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J128" s="1">
         <v>30</v>
       </c>
-      <c r="K87" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D88" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E88" s="1">
+      <c r="K128" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D129" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E129" s="1">
         <v>31</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H129" t="s">
         <v>1</v>
       </c>
-      <c r="I88" s="1">
+      <c r="I129" s="1">
         <v>1</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J129" s="1">
         <v>31</v>
       </c>
-      <c r="K88" t="s">
+      <c r="K129" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D89" t="s">
+    <row r="130" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D130" t="s">
         <v>92</v>
       </c>
-      <c r="E89" s="1">
+      <c r="E130" s="1">
         <v>32</v>
       </c>
-      <c r="J89" s="1">
+      <c r="J130" s="1">
         <v>32</v>
       </c>
-      <c r="K89" t="s">
+      <c r="K130" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D90" t="s">
+    <row r="131" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D131" t="s">
         <v>91</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E131" s="1">
         <v>33</v>
       </c>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1">
+      <c r="I131" s="1"/>
+      <c r="J131" s="1">
         <v>33</v>
       </c>
-      <c r="K90" s="2" t="s">
+      <c r="K131" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D91" t="s">
+    <row r="132" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D132" t="s">
         <v>77</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E132" s="1">
         <v>34</v>
       </c>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1">
+      <c r="I132" s="1"/>
+      <c r="J132" s="1">
         <v>34</v>
       </c>
-      <c r="K91" s="2" t="s">
+      <c r="K132" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D92" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E92" s="1">
+    <row r="133" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D133" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E133" s="1">
         <v>35</v>
       </c>
-      <c r="G92" s="7"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1">
+      <c r="G133" s="7"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1">
         <v>35</v>
       </c>
-      <c r="K92" s="2" t="s">
+      <c r="K133" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D93" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E93" s="1">
+    <row r="134" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D134" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E134" s="1">
         <v>36</v>
       </c>
-      <c r="G93" s="7"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1">
+      <c r="G134" s="7"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1">
         <v>36</v>
       </c>
-      <c r="K93" t="s">
+      <c r="K134" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D94" t="s">
+    <row r="135" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D135" t="s">
         <v>74</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E135" s="1">
         <v>37</v>
       </c>
-      <c r="G94" s="7"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1">
+      <c r="G135" s="7"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1">
         <v>37</v>
       </c>
-      <c r="K94" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D95" t="s">
+      <c r="K135" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D136" t="s">
         <v>98</v>
       </c>
-      <c r="E95" s="1">
+      <c r="E136" s="1">
         <v>38</v>
       </c>
-      <c r="G95" s="7"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1">
+      <c r="G136" s="7"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1">
         <v>38</v>
       </c>
-      <c r="K95" s="2" t="s">
+      <c r="K136" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="96" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D96" t="s">
+    <row r="137" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D137" t="s">
         <v>84</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E137" s="1">
         <v>39</v>
       </c>
-      <c r="G96" s="7"/>
-      <c r="H96" t="s">
+      <c r="G137" s="7"/>
+      <c r="H137" t="s">
         <v>2</v>
       </c>
-      <c r="I96" s="1">
+      <c r="I137" s="1">
         <v>2</v>
       </c>
-      <c r="J96" s="1">
+      <c r="J137" s="1">
         <v>39</v>
       </c>
-      <c r="K96" t="s">
+      <c r="K137" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="4:11" x14ac:dyDescent="0.65">
-      <c r="D97" t="s">
+    <row r="138" spans="4:11" x14ac:dyDescent="0.65">
+      <c r="D138" t="s">
         <v>99</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E138" s="1">
         <v>40</v>
       </c>
-      <c r="G97" s="7"/>
-      <c r="J97" s="1">
+      <c r="G138" s="7"/>
+      <c r="J138" s="1">
         <v>40</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K138" t="s">
         <v>30</v>
       </c>
     </row>

--- a/documentation/pinout.xlsx
+++ b/documentation/pinout.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -525,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -550,6 +550,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2119,7 +2122,7 @@
       <c r="D67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H67" s="13">
+      <c r="H67" s="14">
         <v>2</v>
       </c>
       <c r="J67" t="s">

--- a/documentation/pinout.xlsx
+++ b/documentation/pinout.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="140">
   <si>
     <t>Pin</t>
   </si>
@@ -450,7 +450,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,12 +473,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF6A9955"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -525,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -537,9 +531,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -835,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
   <cols>
     <col min="4" max="4" width="10.04296875" customWidth="1"/>
@@ -845,7 +836,7 @@
     <col min="14" max="14" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:12" x14ac:dyDescent="0.65">
+    <row r="1" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
@@ -858,8 +849,14 @@
       <c r="L1" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C2" s="1">
         <v>1</v>
       </c>
@@ -872,8 +869,15 @@
       <c r="L2" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C3" s="1">
         <v>2</v>
       </c>
@@ -895,8 +899,20 @@
       <c r="L3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>4</v>
+      </c>
+      <c r="R3" s="1">
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C4" s="1">
         <v>3</v>
       </c>
@@ -918,8 +934,15 @@
       <c r="L4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1">
+        <v>3</v>
+      </c>
+      <c r="S4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C5" s="1">
         <v>4</v>
       </c>
@@ -932,8 +955,15 @@
       <c r="L5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1">
+        <v>4</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C6" s="1">
         <v>5</v>
       </c>
@@ -958,8 +988,20 @@
       <c r="L6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>37</v>
+      </c>
+      <c r="R6" s="1">
+        <v>5</v>
+      </c>
+      <c r="S6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C7" s="1">
         <v>6</v>
       </c>
@@ -978,8 +1020,15 @@
       <c r="L7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1">
+        <v>6</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C8" s="1">
         <v>7</v>
       </c>
@@ -995,8 +1044,20 @@
       <c r="L8" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>3</v>
+      </c>
+      <c r="R8" s="1">
+        <v>7</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C9" s="1">
         <v>8</v>
       </c>
@@ -1018,8 +1079,20 @@
       <c r="L9" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>24</v>
+      </c>
+      <c r="R9" s="1">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C10" s="1">
         <v>9</v>
       </c>
@@ -1032,7 +1105,7 @@
       <c r="F10" t="s">
         <v>110</v>
       </c>
-      <c r="H10" s="8"/>
+      <c r="H10" s="7"/>
       <c r="I10">
         <v>2</v>
       </c>
@@ -1042,15 +1115,27 @@
       <c r="L10" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P10" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>23</v>
+      </c>
+      <c r="R10" s="1">
+        <v>9</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="8"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="2">
         <v>4</v>
       </c>
@@ -1060,8 +1145,20 @@
       <c r="L11" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>6</v>
+      </c>
+      <c r="R11" s="1">
+        <v>10</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C12" s="1">
         <v>11</v>
       </c>
@@ -1074,7 +1171,7 @@
       <c r="F12" t="s">
         <v>108</v>
       </c>
-      <c r="H12" s="8"/>
+      <c r="H12" s="7"/>
       <c r="I12">
         <v>6</v>
       </c>
@@ -1084,8 +1181,20 @@
       <c r="L12" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P12" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>26</v>
+      </c>
+      <c r="R12" s="1">
+        <v>11</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C13" s="1">
         <v>12</v>
       </c>
@@ -1098,7 +1207,7 @@
       <c r="F13" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="8"/>
+      <c r="H13" s="7"/>
       <c r="I13">
         <v>5</v>
       </c>
@@ -1108,15 +1217,27 @@
       <c r="L13" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P13" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>25</v>
+      </c>
+      <c r="R13" s="1">
+        <v>12</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C14" s="1">
         <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="8"/>
+      <c r="H14" s="7"/>
       <c r="I14" s="2">
         <v>7</v>
       </c>
@@ -1126,8 +1247,20 @@
       <c r="L14" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>13</v>
+      </c>
+      <c r="R14" s="1">
+        <v>13</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C15" s="1">
         <v>14</v>
       </c>
@@ -1140,7 +1273,7 @@
       <c r="F15" t="s">
         <v>111</v>
       </c>
-      <c r="H15" s="8"/>
+      <c r="H15" s="7"/>
       <c r="I15">
         <v>9</v>
       </c>
@@ -1150,8 +1283,20 @@
       <c r="L15" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.65">
+      <c r="P15" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>28</v>
+      </c>
+      <c r="R15" s="1">
+        <v>14</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C16" s="1">
         <v>15</v>
       </c>
@@ -1164,7 +1309,7 @@
       <c r="F16" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="8"/>
+      <c r="H16" s="7"/>
       <c r="I16">
         <v>8</v>
       </c>
@@ -1174,15 +1319,27 @@
       <c r="L16" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P16" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>27</v>
+      </c>
+      <c r="R16" s="1">
+        <v>15</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C17" s="1">
         <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="8"/>
+      <c r="H17" s="7"/>
       <c r="I17" s="2">
         <v>10</v>
       </c>
@@ -1192,15 +1349,27 @@
       <c r="L17" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>14</v>
+      </c>
+      <c r="R17" s="1">
+        <v>16</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C18" s="1">
         <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="8"/>
+      <c r="H18" s="7"/>
       <c r="I18">
         <v>12</v>
       </c>
@@ -1210,15 +1379,27 @@
       <c r="L18" s="1">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P18" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>16</v>
+      </c>
+      <c r="R18" s="1">
+        <v>17</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C19" s="1">
         <v>18</v>
       </c>
       <c r="D19" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="8"/>
+      <c r="H19" s="7"/>
       <c r="I19">
         <v>11</v>
       </c>
@@ -1228,15 +1409,27 @@
       <c r="L19" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P19" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>15</v>
+      </c>
+      <c r="R19" s="1">
+        <v>18</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C20" s="1">
         <v>19</v>
       </c>
       <c r="D20" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="8"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="2">
         <v>13</v>
       </c>
@@ -1246,15 +1439,27 @@
       <c r="L20" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>21</v>
+      </c>
+      <c r="R20" s="1">
+        <v>19</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C21" s="1">
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="8"/>
+      <c r="H21" s="7"/>
       <c r="I21">
         <v>15</v>
       </c>
@@ -1264,15 +1469,27 @@
       <c r="L21" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P21" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>18</v>
+      </c>
+      <c r="R21" s="1">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C22" s="1">
         <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="8"/>
+      <c r="H22" s="7"/>
       <c r="I22">
         <v>14</v>
       </c>
@@ -1282,15 +1499,27 @@
       <c r="L22" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P22" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>17</v>
+      </c>
+      <c r="R22" s="1">
+        <v>21</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C23" s="1">
         <v>22</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="7"/>
       <c r="I23" s="2">
         <v>16</v>
       </c>
@@ -1300,15 +1529,27 @@
       <c r="L23" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>22</v>
+      </c>
+      <c r="R23" s="1">
+        <v>22</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C24" s="1">
         <v>23</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="8"/>
+      <c r="H24" s="7"/>
       <c r="I24" s="5" t="s">
         <v>65</v>
       </c>
@@ -1318,15 +1559,27 @@
       <c r="L24" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>19</v>
+      </c>
+      <c r="R24" s="1">
+        <v>23</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C25" s="1">
         <v>24</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="8"/>
+      <c r="H25" s="7"/>
       <c r="I25" t="s">
         <v>116</v>
       </c>
@@ -1336,30 +1589,54 @@
       <c r="L25" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P25" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>20</v>
+      </c>
+      <c r="R25" s="1">
+        <v>24</v>
+      </c>
+      <c r="S25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C26" s="1">
         <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H26" s="8"/>
+      <c r="H26" s="7"/>
       <c r="K26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>29</v>
+      </c>
+      <c r="R26" s="1">
+        <v>25</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C27" s="1">
         <v>26</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="8"/>
+      <c r="H27" s="7"/>
       <c r="I27" t="s">
         <v>117</v>
       </c>
@@ -1369,15 +1646,27 @@
       <c r="L27" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>7</v>
+      </c>
+      <c r="R27" s="1">
+        <v>26</v>
+      </c>
+      <c r="S27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C28" s="1">
         <v>27</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H28" s="8"/>
+      <c r="H28" s="7"/>
       <c r="I28" t="s">
         <v>118</v>
       </c>
@@ -1387,53 +1676,91 @@
       <c r="L28" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P28" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>8</v>
+      </c>
+      <c r="R28" s="1">
+        <v>27</v>
+      </c>
+      <c r="S28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C29" s="1">
         <v>28</v>
       </c>
       <c r="D29" t="s">
         <v>44</v>
       </c>
-      <c r="H29" s="8"/>
+      <c r="H29" s="7"/>
       <c r="K29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="L29" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1">
+        <v>28</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C30" s="1">
         <v>29</v>
       </c>
       <c r="D30" t="s">
         <v>44</v>
       </c>
-      <c r="H30" s="8"/>
+      <c r="H30" s="7"/>
       <c r="K30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1">
+        <v>29</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C31" s="1">
         <v>30</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H31" s="8"/>
+      <c r="H31" s="7"/>
       <c r="K31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L31" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.65">
+      <c r="P31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>36</v>
+      </c>
+      <c r="R31" s="1">
+        <v>30</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.65">
       <c r="C32" s="1">
         <v>31</v>
       </c>
@@ -1441,7 +1768,7 @@
         <v>4</v>
       </c>
       <c r="G32" s="1"/>
-      <c r="H32" s="8"/>
+      <c r="H32" s="7"/>
       <c r="I32">
         <v>28</v>
       </c>
@@ -1454,8 +1781,20 @@
       <c r="M32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="P32" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>1</v>
+      </c>
+      <c r="R32" s="1">
+        <v>31</v>
+      </c>
+      <c r="S32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C33" s="1">
         <v>32</v>
       </c>
@@ -1463,7 +1802,7 @@
         <v>3</v>
       </c>
       <c r="G33" s="1"/>
-      <c r="H33" s="8"/>
+      <c r="H33" s="7"/>
       <c r="I33">
         <v>29</v>
       </c>
@@ -1473,8 +1812,14 @@
       <c r="L33" s="1">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="R33" s="1">
+        <v>32</v>
+      </c>
+      <c r="S33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C34" s="1">
         <v>33</v>
       </c>
@@ -1482,15 +1827,22 @@
         <v>3</v>
       </c>
       <c r="G34" s="1"/>
-      <c r="H34" s="8"/>
+      <c r="H34" s="7"/>
       <c r="K34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L34" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1">
+        <v>33</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C35" s="1">
         <v>34</v>
       </c>
@@ -1498,15 +1850,22 @@
         <v>4</v>
       </c>
       <c r="G35" s="1"/>
-      <c r="H35" s="8"/>
+      <c r="H35" s="7"/>
       <c r="K35" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1">
+        <v>34</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C36" s="1">
         <v>35</v>
       </c>
@@ -1514,15 +1873,22 @@
         <v>45</v>
       </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="8"/>
+      <c r="H36" s="7"/>
       <c r="K36" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L36" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1">
+        <v>35</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C37" s="1">
         <v>36</v>
       </c>
@@ -1530,15 +1896,22 @@
         <v>45</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="8"/>
+      <c r="H37" s="7"/>
       <c r="K37" t="s">
         <v>28</v>
       </c>
       <c r="L37" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1">
+        <v>36</v>
+      </c>
+      <c r="S37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C38" s="1">
         <v>37</v>
       </c>
@@ -1546,15 +1919,22 @@
         <v>3</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="8"/>
+      <c r="H38" s="7"/>
       <c r="K38" s="2" t="s">
         <v>4</v>
       </c>
       <c r="L38" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1">
+        <v>37</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C39" s="1">
         <v>38</v>
       </c>
@@ -1562,15 +1942,22 @@
         <v>104</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="8"/>
+      <c r="H39" s="7"/>
       <c r="K39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L39" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1">
+        <v>38</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C40" s="1">
         <v>39</v>
       </c>
@@ -1578,7 +1965,7 @@
         <v>104</v>
       </c>
       <c r="G40" s="1"/>
-      <c r="H40" s="8"/>
+      <c r="H40" s="7"/>
       <c r="I40">
         <v>35</v>
       </c>
@@ -1591,8 +1978,20 @@
       <c r="M40" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="P40" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>2</v>
+      </c>
+      <c r="R40" s="1">
+        <v>39</v>
+      </c>
+      <c r="S40" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C41" s="1">
         <v>40</v>
       </c>
@@ -1600,7 +1999,7 @@
         <v>4</v>
       </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="8"/>
+      <c r="H41" s="7"/>
       <c r="I41">
         <v>36</v>
       </c>
@@ -1610,23 +2009,29 @@
       <c r="L41" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="R41" s="1">
+        <v>40</v>
+      </c>
+      <c r="S41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A42" s="1"/>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A43" s="1"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="H43" s="7"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C44" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H44" s="12"/>
+      <c r="H44" s="11"/>
       <c r="K44" s="6" t="s">
         <v>119</v>
       </c>
@@ -1634,14 +2039,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.65">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C45" s="1">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="13">
+      <c r="H45" s="12">
         <v>28</v>
       </c>
       <c r="K45" t="s">
@@ -1650,9 +2055,9 @@
       <c r="L45" s="1">
         <v>1</v>
       </c>
-      <c r="M45" s="8"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="M45" s="7"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C46" s="1">
         <v>2</v>
       </c>
@@ -1665,19 +2070,19 @@
       <c r="F46" t="s">
         <v>107</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H46" s="12">
         <v>35</v>
       </c>
-      <c r="J46" s="8"/>
+      <c r="J46" s="7"/>
       <c r="K46" t="s">
         <v>2</v>
       </c>
       <c r="L46" s="1">
         <v>2</v>
       </c>
-      <c r="M46" s="8"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="M46" s="7"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C47" s="1">
         <v>3</v>
       </c>
@@ -1690,36 +2095,36 @@
       <c r="F47" t="s">
         <v>107</v>
       </c>
-      <c r="H47" s="13">
+      <c r="H47" s="12">
         <v>37</v>
       </c>
-      <c r="J47" s="8"/>
+      <c r="J47" s="7"/>
       <c r="K47" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L47" s="1">
         <v>3</v>
       </c>
-      <c r="M47" s="8"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.65">
+      <c r="M47" s="7"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C48" s="1">
         <v>4</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H48" s="13">
+      <c r="H48" s="12">
         <v>38</v>
       </c>
-      <c r="J48" s="8"/>
+      <c r="J48" s="7"/>
       <c r="K48" t="s">
         <v>76</v>
       </c>
       <c r="L48" s="1">
         <v>4</v>
       </c>
-      <c r="M48" s="8"/>
+      <c r="M48" s="7"/>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C49" s="1">
@@ -1734,15 +2139,15 @@
       <c r="F49" t="s">
         <v>109</v>
       </c>
-      <c r="H49" s="13"/>
-      <c r="J49" s="8"/>
+      <c r="H49" s="12"/>
+      <c r="J49" s="7"/>
       <c r="K49" s="2" t="s">
         <v>4</v>
       </c>
       <c r="L49" s="1">
         <v>5</v>
       </c>
-      <c r="M49" s="8"/>
+      <c r="M49" s="7"/>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C50" s="1">
@@ -1757,15 +2162,15 @@
       <c r="F50" t="s">
         <v>109</v>
       </c>
-      <c r="H50" s="13"/>
-      <c r="J50" s="8"/>
+      <c r="H50" s="12"/>
+      <c r="J50" s="7"/>
       <c r="K50" s="2" t="s">
         <v>4</v>
       </c>
       <c r="L50" s="1">
         <v>6</v>
       </c>
-      <c r="M50" s="8"/>
+      <c r="M50" s="7"/>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C51" s="1">
@@ -1774,7 +2179,7 @@
       <c r="D51" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H51" s="13"/>
+      <c r="H51" s="12"/>
       <c r="J51" t="s">
         <v>50</v>
       </c>
@@ -1784,7 +2189,7 @@
       <c r="L51" s="1">
         <v>7</v>
       </c>
-      <c r="M51" s="8"/>
+      <c r="M51" s="7"/>
     </row>
     <row r="52" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C52" s="1">
@@ -1799,7 +2204,7 @@
       <c r="F52" t="s">
         <v>110</v>
       </c>
-      <c r="H52" s="13"/>
+      <c r="H52" s="12"/>
       <c r="J52" t="s">
         <v>53</v>
       </c>
@@ -1809,7 +2214,7 @@
       <c r="L52" s="1">
         <v>8</v>
       </c>
-      <c r="M52" s="8"/>
+      <c r="M52" s="7"/>
     </row>
     <row r="53" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C53" s="1">
@@ -1824,7 +2229,7 @@
       <c r="F53" t="s">
         <v>110</v>
       </c>
-      <c r="H53" s="13"/>
+      <c r="H53" s="12"/>
       <c r="J53" t="s">
         <v>56</v>
       </c>
@@ -1834,7 +2239,7 @@
       <c r="L53" s="1">
         <v>9</v>
       </c>
-      <c r="M53" s="8"/>
+      <c r="M53" s="7"/>
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C54" s="1">
@@ -1843,7 +2248,7 @@
       <c r="D54" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H54" s="13"/>
+      <c r="H54" s="12"/>
       <c r="J54" t="s">
         <v>58</v>
       </c>
@@ -1853,7 +2258,7 @@
       <c r="L54" s="1">
         <v>10</v>
       </c>
-      <c r="M54" s="8"/>
+      <c r="M54" s="7"/>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C55" s="1">
@@ -1868,7 +2273,7 @@
       <c r="F55" t="s">
         <v>108</v>
       </c>
-      <c r="H55" s="13"/>
+      <c r="H55" s="12"/>
       <c r="J55" t="s">
         <v>89</v>
       </c>
@@ -1878,7 +2283,7 @@
       <c r="L55" s="1">
         <v>11</v>
       </c>
-      <c r="M55" s="8"/>
+      <c r="M55" s="7"/>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C56" s="1">
@@ -1893,7 +2298,7 @@
       <c r="F56" t="s">
         <v>108</v>
       </c>
-      <c r="H56" s="13"/>
+      <c r="H56" s="12"/>
       <c r="J56" t="s">
         <v>75</v>
       </c>
@@ -1903,7 +2308,7 @@
       <c r="L56" s="1">
         <v>12</v>
       </c>
-      <c r="M56" s="8"/>
+      <c r="M56" s="7"/>
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C57" s="1">
@@ -1912,7 +2317,7 @@
       <c r="D57" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="13"/>
+      <c r="H57" s="12"/>
       <c r="J57" s="2" t="s">
         <v>3</v>
       </c>
@@ -1922,7 +2327,7 @@
       <c r="L57" s="1">
         <v>13</v>
       </c>
-      <c r="M57" s="8"/>
+      <c r="M57" s="7"/>
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C58" s="1">
@@ -1937,7 +2342,7 @@
       <c r="F58" t="s">
         <v>111</v>
       </c>
-      <c r="H58" s="13"/>
+      <c r="H58" s="12"/>
       <c r="J58" s="2" t="s">
         <v>3</v>
       </c>
@@ -1947,7 +2352,7 @@
       <c r="L58" s="1">
         <v>14</v>
       </c>
-      <c r="M58" s="8"/>
+      <c r="M58" s="7"/>
     </row>
     <row r="59" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C59" s="1">
@@ -1962,7 +2367,7 @@
       <c r="F59" t="s">
         <v>111</v>
       </c>
-      <c r="H59" s="13">
+      <c r="H59" s="12">
         <v>11</v>
       </c>
       <c r="J59" t="s">
@@ -1974,7 +2379,7 @@
       <c r="L59" s="1">
         <v>15</v>
       </c>
-      <c r="M59" s="8"/>
+      <c r="M59" s="7"/>
     </row>
     <row r="60" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C60" s="1">
@@ -1983,7 +2388,7 @@
       <c r="D60" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H60" s="13">
+      <c r="H60" s="12">
         <v>12</v>
       </c>
       <c r="J60" t="s">
@@ -1995,7 +2400,7 @@
       <c r="L60" s="1">
         <v>16</v>
       </c>
-      <c r="M60" s="8"/>
+      <c r="M60" s="7"/>
     </row>
     <row r="61" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C61" s="1">
@@ -2004,7 +2409,7 @@
       <c r="D61" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H61" s="13">
+      <c r="H61" s="12">
         <v>14</v>
       </c>
       <c r="J61" t="s">
@@ -2016,7 +2421,7 @@
       <c r="L61" s="1">
         <v>17</v>
       </c>
-      <c r="M61" s="8"/>
+      <c r="M61" s="7"/>
     </row>
     <row r="62" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C62" s="1">
@@ -2025,7 +2430,7 @@
       <c r="D62" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="13">
+      <c r="H62" s="12">
         <v>15</v>
       </c>
       <c r="J62" t="s">
@@ -2037,7 +2442,7 @@
       <c r="L62" s="1">
         <v>18</v>
       </c>
-      <c r="M62" s="8"/>
+      <c r="M62" s="7"/>
     </row>
     <row r="63" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C63" s="1">
@@ -2046,7 +2451,7 @@
       <c r="D63" t="s">
         <v>43</v>
       </c>
-      <c r="H63" s="13"/>
+      <c r="H63" s="12"/>
       <c r="J63" t="s">
         <v>52</v>
       </c>
@@ -2056,7 +2461,7 @@
       <c r="L63" s="1">
         <v>19</v>
       </c>
-      <c r="M63" s="8"/>
+      <c r="M63" s="7"/>
     </row>
     <row r="64" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C64" s="1">
@@ -2065,7 +2470,7 @@
       <c r="D64" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H64" s="13"/>
+      <c r="H64" s="12"/>
       <c r="J64" t="s">
         <v>49</v>
       </c>
@@ -2075,7 +2480,7 @@
       <c r="L64" s="1">
         <v>20</v>
       </c>
-      <c r="M64" s="8"/>
+      <c r="M64" s="7"/>
     </row>
     <row r="65" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C65" s="1">
@@ -2084,7 +2489,7 @@
       <c r="D65" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H65" s="13"/>
+      <c r="H65" s="12"/>
       <c r="J65" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,7 +2499,7 @@
       <c r="L65" s="1">
         <v>21</v>
       </c>
-      <c r="M65" s="8"/>
+      <c r="M65" s="7"/>
     </row>
     <row r="66" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C66" s="1">
@@ -2103,7 +2508,7 @@
       <c r="D66" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H66" s="13"/>
+      <c r="H66" s="12"/>
       <c r="J66" s="2" t="s">
         <v>3</v>
       </c>
@@ -2113,7 +2518,7 @@
       <c r="L66" s="1">
         <v>22</v>
       </c>
-      <c r="M66" s="8"/>
+      <c r="M66" s="7"/>
     </row>
     <row r="67" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C67" s="1">
@@ -2122,7 +2527,7 @@
       <c r="D67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H67" s="14">
+      <c r="H67" s="13">
         <v>2</v>
       </c>
       <c r="J67" t="s">
@@ -2134,7 +2539,7 @@
       <c r="L67" s="1">
         <v>23</v>
       </c>
-      <c r="M67" s="8"/>
+      <c r="M67" s="7"/>
     </row>
     <row r="68" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C68" s="1">
@@ -2143,7 +2548,7 @@
       <c r="D68" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="13">
+      <c r="H68" s="12">
         <v>3</v>
       </c>
       <c r="J68" t="s">
@@ -2155,7 +2560,7 @@
       <c r="L68" s="1">
         <v>24</v>
       </c>
-      <c r="M68" s="8"/>
+      <c r="M68" s="7"/>
     </row>
     <row r="69" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C69" s="1">
@@ -2164,7 +2569,7 @@
       <c r="D69" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H69" s="13">
+      <c r="H69" s="12">
         <v>5</v>
       </c>
       <c r="J69" t="s">
@@ -2176,7 +2581,7 @@
       <c r="L69" s="1">
         <v>25</v>
       </c>
-      <c r="M69" s="8"/>
+      <c r="M69" s="7"/>
     </row>
     <row r="70" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C70" s="1">
@@ -2185,7 +2590,7 @@
       <c r="D70" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H70" s="13">
+      <c r="H70" s="12">
         <v>6</v>
       </c>
       <c r="J70" t="s">
@@ -2197,7 +2602,7 @@
       <c r="L70" s="1">
         <v>26</v>
       </c>
-      <c r="M70" s="8"/>
+      <c r="M70" s="7"/>
     </row>
     <row r="71" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C71" s="1">
@@ -2206,7 +2611,7 @@
       <c r="D71" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H71" s="13">
+      <c r="H71" s="12">
         <v>8</v>
       </c>
       <c r="J71" t="s">
@@ -2218,7 +2623,7 @@
       <c r="L71" s="1">
         <v>27</v>
       </c>
-      <c r="M71" s="8"/>
+      <c r="M71" s="7"/>
     </row>
     <row r="72" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C72" s="1">
@@ -2227,7 +2632,7 @@
       <c r="D72" t="s">
         <v>44</v>
       </c>
-      <c r="H72" s="13">
+      <c r="H72" s="12">
         <v>9</v>
       </c>
       <c r="J72" t="s">
@@ -2239,7 +2644,7 @@
       <c r="L72" s="1">
         <v>28</v>
       </c>
-      <c r="M72" s="8"/>
+      <c r="M72" s="7"/>
     </row>
     <row r="73" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C73" s="1">
@@ -2248,17 +2653,17 @@
       <c r="D73" t="s">
         <v>44</v>
       </c>
-      <c r="H73" s="13">
+      <c r="H73" s="12">
         <v>33</v>
       </c>
-      <c r="J73" s="8"/>
+      <c r="J73" s="7"/>
       <c r="K73" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L73" s="1">
         <v>29</v>
       </c>
-      <c r="M73" s="8"/>
+      <c r="M73" s="7"/>
     </row>
     <row r="74" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C74" s="1">
@@ -2267,8 +2672,8 @@
       <c r="D74" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H74" s="13"/>
-      <c r="J74" s="10" t="s">
+      <c r="H74" s="12"/>
+      <c r="J74" s="9" t="s">
         <v>78</v>
       </c>
       <c r="K74" t="s">
@@ -2277,7 +2682,7 @@
       <c r="L74" s="1">
         <v>30</v>
       </c>
-      <c r="M74" s="8"/>
+      <c r="M74" s="7"/>
     </row>
     <row r="75" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C75" s="1">
@@ -2287,15 +2692,15 @@
         <v>4</v>
       </c>
       <c r="G75" s="1"/>
-      <c r="H75" s="13"/>
-      <c r="J75" s="8"/>
+      <c r="H75" s="12"/>
+      <c r="J75" s="7"/>
       <c r="K75" s="2" t="s">
         <v>4</v>
       </c>
       <c r="L75" s="1">
         <v>31</v>
       </c>
-      <c r="M75" s="8"/>
+      <c r="M75" s="7"/>
     </row>
     <row r="76" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C76" s="1">
@@ -2305,8 +2710,8 @@
         <v>3</v>
       </c>
       <c r="G76" s="1"/>
-      <c r="H76" s="13"/>
-      <c r="J76" s="10" t="s">
+      <c r="H76" s="12"/>
+      <c r="J76" s="9" t="s">
         <v>92</v>
       </c>
       <c r="K76" t="s">
@@ -2315,7 +2720,7 @@
       <c r="L76" s="1">
         <v>32</v>
       </c>
-      <c r="M76" s="8"/>
+      <c r="M76" s="7"/>
     </row>
     <row r="77" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C77" s="1">
@@ -2325,8 +2730,8 @@
         <v>3</v>
       </c>
       <c r="G77" s="1"/>
-      <c r="H77" s="13"/>
-      <c r="J77" s="10" t="s">
+      <c r="H77" s="12"/>
+      <c r="J77" s="9" t="s">
         <v>91</v>
       </c>
       <c r="K77" t="s">
@@ -2335,7 +2740,7 @@
       <c r="L77" s="1">
         <v>33</v>
       </c>
-      <c r="M77" s="8"/>
+      <c r="M77" s="7"/>
     </row>
     <row r="78" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C78" s="1">
@@ -2345,8 +2750,8 @@
         <v>4</v>
       </c>
       <c r="G78" s="1"/>
-      <c r="H78" s="13"/>
-      <c r="J78" s="10" t="s">
+      <c r="H78" s="12"/>
+      <c r="J78" s="9" t="s">
         <v>77</v>
       </c>
       <c r="K78" t="s">
@@ -2355,7 +2760,7 @@
       <c r="L78" s="1">
         <v>34</v>
       </c>
-      <c r="M78" s="8"/>
+      <c r="M78" s="7"/>
     </row>
     <row r="79" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C79" s="1">
@@ -2365,15 +2770,15 @@
         <v>45</v>
       </c>
       <c r="G79" s="1"/>
-      <c r="H79" s="13"/>
-      <c r="J79" s="8"/>
+      <c r="H79" s="12"/>
+      <c r="J79" s="7"/>
       <c r="K79" s="2" t="s">
         <v>4</v>
       </c>
       <c r="L79" s="1">
         <v>35</v>
       </c>
-      <c r="M79" s="8"/>
+      <c r="M79" s="7"/>
     </row>
     <row r="80" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C80" s="1">
@@ -2383,17 +2788,17 @@
         <v>45</v>
       </c>
       <c r="G80" s="1"/>
-      <c r="H80" s="13">
+      <c r="H80" s="12">
         <v>32</v>
       </c>
-      <c r="J80" s="8"/>
+      <c r="J80" s="7"/>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L80" s="1">
         <v>36</v>
       </c>
-      <c r="M80" s="8"/>
+      <c r="M80" s="7"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.65">
       <c r="C81" s="1">
@@ -2403,8 +2808,8 @@
         <v>3</v>
       </c>
       <c r="G81" s="1"/>
-      <c r="H81" s="13"/>
-      <c r="J81" s="11" t="s">
+      <c r="H81" s="12"/>
+      <c r="J81" s="10" t="s">
         <v>74</v>
       </c>
       <c r="K81" t="s">
@@ -2413,7 +2818,7 @@
       <c r="L81" s="1">
         <v>37</v>
       </c>
-      <c r="M81" s="8"/>
+      <c r="M81" s="7"/>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.65">
       <c r="C82" s="1">
@@ -2423,8 +2828,8 @@
         <v>104</v>
       </c>
       <c r="G82" s="1"/>
-      <c r="H82" s="13"/>
-      <c r="J82" s="11" t="s">
+      <c r="H82" s="12"/>
+      <c r="J82" s="10" t="s">
         <v>98</v>
       </c>
       <c r="K82" t="s">
@@ -2433,7 +2838,7 @@
       <c r="L82" s="1">
         <v>38</v>
       </c>
-      <c r="M82" s="8"/>
+      <c r="M82" s="7"/>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.65">
       <c r="C83" s="1">
@@ -2443,10 +2848,10 @@
         <v>104</v>
       </c>
       <c r="G83" s="1"/>
-      <c r="H83" s="13">
+      <c r="H83" s="12">
         <v>24</v>
       </c>
-      <c r="J83" s="8" t="s">
+      <c r="J83" s="7" t="s">
         <v>84</v>
       </c>
       <c r="K83" t="s">
@@ -2455,7 +2860,7 @@
       <c r="L83" s="1">
         <v>39</v>
       </c>
-      <c r="M83" s="8"/>
+      <c r="M83" s="7"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.65">
       <c r="C84" s="1">
@@ -2465,8 +2870,8 @@
         <v>4</v>
       </c>
       <c r="G84" s="1"/>
-      <c r="H84" s="13"/>
-      <c r="J84" s="11" t="s">
+      <c r="H84" s="12"/>
+      <c r="J84" s="10" t="s">
         <v>99</v>
       </c>
       <c r="K84" t="s">
@@ -2475,11 +2880,11 @@
       <c r="L84" s="1">
         <v>40</v>
       </c>
-      <c r="M84" s="8"/>
+      <c r="M84" s="7"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A85" s="1"/>
-      <c r="H85" s="13"/>
+      <c r="H85" s="12"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A86" s="4" t="s">
@@ -2490,7 +2895,7 @@
       <c r="D86" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H86" s="13"/>
+      <c r="H86" s="12"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A87" t="s">
@@ -2505,7 +2910,7 @@
       <c r="D87" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H87" s="13"/>
+      <c r="H87" s="12"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A88" t="s">
@@ -2523,7 +2928,7 @@
       <c r="E88" t="s">
         <v>116</v>
       </c>
-      <c r="H88" s="8"/>
+      <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A89" t="s">
@@ -2541,7 +2946,7 @@
       <c r="E89" t="s">
         <v>117</v>
       </c>
-      <c r="H89" s="8"/>
+      <c r="H89" s="7"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A90" t="s">
@@ -2559,7 +2964,7 @@
       <c r="E90" t="s">
         <v>118</v>
       </c>
-      <c r="H90" s="8"/>
+      <c r="H90" s="7"/>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.65">
       <c r="A91" t="s">
@@ -2611,42 +3016,40 @@
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.65">
-      <c r="D96" s="9"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.65">
-      <c r="D97" s="9"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="D96" s="8"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="D97" s="8"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A98" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H98" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="H98" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D99" t="s">
         <v>1</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
       </c>
-      <c r="G99" s="7"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1">
+      <c r="H99" t="s">
         <v>1</v>
       </c>
-      <c r="K99" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="I99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A100" t="s">
         <v>76</v>
       </c>
@@ -2661,19 +3064,13 @@
       </c>
       <c r="G100" s="7"/>
       <c r="H100" t="s">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="I100" s="1">
-        <v>4</v>
-      </c>
-      <c r="J100" s="1">
         <v>2</v>
       </c>
-      <c r="K100" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A101" t="s">
         <v>71</v>
       </c>
@@ -2687,15 +3084,14 @@
         <v>3</v>
       </c>
       <c r="G101" s="7"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1">
-        <v>3</v>
-      </c>
-      <c r="K101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="H101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A102" t="s">
         <v>72</v>
       </c>
@@ -2709,15 +3105,14 @@
         <v>4</v>
       </c>
       <c r="G102" s="7"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1">
-        <v>4</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.65">
+      <c r="H102" t="s">
+        <v>76</v>
+      </c>
+      <c r="I102" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A103" t="s">
         <v>73</v>
       </c>
@@ -2731,20 +3126,14 @@
         <v>5</v>
       </c>
       <c r="G103" s="7"/>
-      <c r="H103" t="s">
-        <v>74</v>
+      <c r="H103" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="I103" s="1">
-        <v>37</v>
-      </c>
-      <c r="J103" s="1">
         <v>5</v>
       </c>
-      <c r="K103" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A104" t="s">
         <v>56</v>
       </c>
@@ -2758,15 +3147,14 @@
         <v>6</v>
       </c>
       <c r="G104" s="7"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1">
+      <c r="H104" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I104" s="1">
         <v>6</v>
       </c>
-      <c r="K104" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A105" t="s">
         <v>74</v>
       </c>
@@ -2781,19 +3169,13 @@
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I105" s="1">
-        <v>3</v>
-      </c>
-      <c r="J105" s="1">
         <v>7</v>
       </c>
-      <c r="K105" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A106" t="s">
         <v>75</v>
       </c>
@@ -2808,19 +3190,13 @@
       </c>
       <c r="G106" s="7"/>
       <c r="H106" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="I106" s="1">
-        <v>24</v>
-      </c>
-      <c r="J106" s="1">
         <v>8</v>
       </c>
-      <c r="K106" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A107" t="s">
         <v>58</v>
       </c>
@@ -2835,19 +3211,13 @@
       </c>
       <c r="G107" s="7"/>
       <c r="H107" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="I107" s="1">
-        <v>23</v>
-      </c>
-      <c r="J107" s="1">
         <v>9</v>
       </c>
-      <c r="K107" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A108" t="s">
         <v>53</v>
       </c>
@@ -2861,20 +3231,14 @@
         <v>10</v>
       </c>
       <c r="G108" s="7"/>
-      <c r="H108" s="2" t="s">
-        <v>3</v>
+      <c r="H108" t="s">
+        <v>122</v>
       </c>
       <c r="I108" s="1">
-        <v>6</v>
-      </c>
-      <c r="J108" s="1">
         <v>10</v>
       </c>
-      <c r="K108" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A109" t="s">
         <v>50</v>
       </c>
@@ -2889,19 +3253,13 @@
       </c>
       <c r="G109" s="7"/>
       <c r="H109" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="I109" s="1">
-        <v>26</v>
-      </c>
-      <c r="J109" s="1">
         <v>11</v>
       </c>
-      <c r="K109" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A110" t="s">
         <v>52</v>
       </c>
@@ -2916,19 +3274,13 @@
       </c>
       <c r="G110" s="7"/>
       <c r="H110" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="I110" s="1">
-        <v>25</v>
-      </c>
-      <c r="J110" s="1">
         <v>12</v>
       </c>
-      <c r="K110" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A111" t="s">
         <v>77</v>
       </c>
@@ -2943,19 +3295,13 @@
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I111" s="1">
         <v>13</v>
       </c>
-      <c r="J111" s="1">
-        <v>13</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A112" t="s">
         <v>78</v>
       </c>
@@ -2969,20 +3315,14 @@
         <v>14</v>
       </c>
       <c r="G112" s="7"/>
-      <c r="H112" t="s">
-        <v>95</v>
+      <c r="H112" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="I112" s="1">
-        <v>28</v>
-      </c>
-      <c r="J112" s="1">
         <v>14</v>
       </c>
-      <c r="K112" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A113" t="s">
         <v>79</v>
       </c>
@@ -2997,19 +3337,13 @@
       </c>
       <c r="G113" s="7"/>
       <c r="H113" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="I113" s="1">
-        <v>27</v>
-      </c>
-      <c r="J113" s="1">
         <v>15</v>
       </c>
-      <c r="K113" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A114" t="s">
         <v>80</v>
       </c>
@@ -3023,20 +3357,14 @@
         <v>16</v>
       </c>
       <c r="G114" s="7"/>
-      <c r="H114" s="2" t="s">
-        <v>3</v>
+      <c r="H114" t="s">
+        <v>126</v>
       </c>
       <c r="I114" s="1">
-        <v>14</v>
-      </c>
-      <c r="J114" s="1">
         <v>16</v>
       </c>
-      <c r="K114" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A115" t="s">
         <v>81</v>
       </c>
@@ -3051,19 +3379,13 @@
       </c>
       <c r="G115" s="7"/>
       <c r="H115" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="I115" s="1">
-        <v>16</v>
-      </c>
-      <c r="J115" s="1">
         <v>17</v>
       </c>
-      <c r="K115" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A116" t="s">
         <v>82</v>
       </c>
@@ -3078,19 +3400,13 @@
       </c>
       <c r="G116" s="7"/>
       <c r="H116" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="I116" s="1">
-        <v>15</v>
-      </c>
-      <c r="J116" s="1">
         <v>18</v>
       </c>
-      <c r="K116" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A117" t="s">
         <v>83</v>
       </c>
@@ -3104,20 +3420,14 @@
         <v>19</v>
       </c>
       <c r="G117" s="7"/>
-      <c r="H117" s="2" t="s">
-        <v>3</v>
+      <c r="H117" t="s">
+        <v>129</v>
       </c>
       <c r="I117" s="1">
-        <v>21</v>
-      </c>
-      <c r="J117" s="1">
         <v>19</v>
       </c>
-      <c r="K117" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A118" t="s">
         <v>84</v>
       </c>
@@ -3132,19 +3442,13 @@
       </c>
       <c r="G118" s="7"/>
       <c r="H118" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="I118" s="1">
-        <v>18</v>
-      </c>
-      <c r="J118" s="1">
         <v>20</v>
       </c>
-      <c r="K118" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A119" t="s">
         <v>3</v>
       </c>
@@ -3158,20 +3462,14 @@
         <v>21</v>
       </c>
       <c r="G119" s="7"/>
-      <c r="H119" t="s">
-        <v>79</v>
+      <c r="H119" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="I119" s="1">
-        <v>17</v>
-      </c>
-      <c r="J119" s="1">
         <v>21</v>
       </c>
-      <c r="K119" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D120" s="2" t="s">
         <v>3</v>
       </c>
@@ -3180,19 +3478,13 @@
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I120" s="1">
         <v>22</v>
       </c>
-      <c r="J120" s="1">
-        <v>22</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D121" t="s">
         <v>83</v>
       </c>
@@ -3200,20 +3492,14 @@
         <v>23</v>
       </c>
       <c r="G121" s="7"/>
-      <c r="H121" t="s">
-        <v>52</v>
+      <c r="H121" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="I121" s="1">
-        <v>19</v>
-      </c>
-      <c r="J121" s="1">
         <v>23</v>
       </c>
-      <c r="K121" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D122" t="s">
         <v>97</v>
       </c>
@@ -3222,19 +3508,13 @@
       </c>
       <c r="G122" s="7"/>
       <c r="H122" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="I122" s="1">
-        <v>20</v>
-      </c>
-      <c r="J122" s="1">
         <v>24</v>
       </c>
-      <c r="K122" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D123" t="s">
         <v>82</v>
       </c>
@@ -3242,20 +3522,14 @@
         <v>25</v>
       </c>
       <c r="G123" s="7"/>
-      <c r="H123" s="2" t="s">
-        <v>3</v>
+      <c r="H123" t="s">
+        <v>132</v>
       </c>
       <c r="I123" s="1">
-        <v>29</v>
-      </c>
-      <c r="J123" s="1">
         <v>25</v>
       </c>
-      <c r="K123" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D124" t="s">
         <v>96</v>
       </c>
@@ -3264,19 +3538,13 @@
       </c>
       <c r="G124" s="7"/>
       <c r="H124" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="I124" s="1">
-        <v>7</v>
-      </c>
-      <c r="J124" s="1">
         <v>26</v>
       </c>
-      <c r="K124" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D125" t="s">
         <v>81</v>
       </c>
@@ -3285,19 +3553,13 @@
       </c>
       <c r="G125" s="7"/>
       <c r="H125" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="I125" s="1">
-        <v>8</v>
-      </c>
-      <c r="J125" s="1">
         <v>27</v>
       </c>
-      <c r="K125" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D126" t="s">
         <v>95</v>
       </c>
@@ -3305,15 +3567,14 @@
         <v>28</v>
       </c>
       <c r="G126" s="7"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1">
+      <c r="H126" t="s">
+        <v>135</v>
+      </c>
+      <c r="I126" s="1">
         <v>28</v>
       </c>
-      <c r="K126" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D127" s="2" t="s">
         <v>3</v>
       </c>
@@ -3321,15 +3582,14 @@
         <v>29</v>
       </c>
       <c r="G127" s="7"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1">
+      <c r="H127" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I127" s="1">
         <v>29</v>
       </c>
-      <c r="K127" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.65">
       <c r="D128" t="s">
         <v>78</v>
       </c>
@@ -3337,84 +3597,74 @@
         <v>30</v>
       </c>
       <c r="G128" s="7"/>
-      <c r="H128" s="2" t="s">
-        <v>3</v>
+      <c r="H128" t="s">
+        <v>136</v>
       </c>
       <c r="I128" s="1">
-        <v>36</v>
-      </c>
-      <c r="J128" s="1">
         <v>30</v>
       </c>
-      <c r="K128" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="129" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="129" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D129" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E129" s="1">
         <v>31</v>
       </c>
-      <c r="H129" t="s">
-        <v>1</v>
+      <c r="G129" s="7"/>
+      <c r="H129" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="I129" s="1">
-        <v>1</v>
-      </c>
-      <c r="J129" s="1">
         <v>31</v>
       </c>
-      <c r="K129" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="130" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="130" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D130" t="s">
         <v>92</v>
       </c>
       <c r="E130" s="1">
         <v>32</v>
       </c>
-      <c r="J130" s="1">
+      <c r="G130" s="7"/>
+      <c r="H130" t="s">
+        <v>137</v>
+      </c>
+      <c r="I130" s="1">
         <v>32</v>
       </c>
-      <c r="K130" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="131" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="131" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D131" t="s">
         <v>91</v>
       </c>
       <c r="E131" s="1">
         <v>33</v>
       </c>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1">
+      <c r="G131" s="7"/>
+      <c r="H131" t="s">
+        <v>138</v>
+      </c>
+      <c r="I131" s="1">
         <v>33</v>
       </c>
-      <c r="K131" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="132" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="132" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D132" t="s">
         <v>77</v>
       </c>
       <c r="E132" s="1">
         <v>34</v>
       </c>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1">
+      <c r="G132" s="7"/>
+      <c r="H132" t="s">
+        <v>139</v>
+      </c>
+      <c r="I132" s="1">
         <v>34</v>
       </c>
-      <c r="K132" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="133" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="133" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D133" s="2" t="s">
         <v>4</v>
       </c>
@@ -3422,15 +3672,14 @@
         <v>35</v>
       </c>
       <c r="G133" s="7"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1">
+      <c r="H133" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I133" s="1">
         <v>35</v>
       </c>
-      <c r="K133" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="134" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="134" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D134" s="2" t="s">
         <v>3</v>
       </c>
@@ -3438,15 +3687,14 @@
         <v>36</v>
       </c>
       <c r="G134" s="7"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1">
+      <c r="H134" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I134" s="1">
         <v>36</v>
       </c>
-      <c r="K134" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="135" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="135" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D135" t="s">
         <v>74</v>
       </c>
@@ -3454,15 +3702,14 @@
         <v>37</v>
       </c>
       <c r="G135" s="7"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1">
+      <c r="H135" t="s">
+        <v>5</v>
+      </c>
+      <c r="I135" s="1">
         <v>37</v>
       </c>
-      <c r="K135" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="136" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D136" t="s">
         <v>98</v>
       </c>
@@ -3470,15 +3717,14 @@
         <v>38</v>
       </c>
       <c r="G136" s="7"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1">
+      <c r="H136" t="s">
+        <v>21</v>
+      </c>
+      <c r="I136" s="1">
         <v>38</v>
       </c>
-      <c r="K136" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="137" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="137" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D137" t="s">
         <v>84</v>
       </c>
@@ -3487,19 +3733,13 @@
       </c>
       <c r="G137" s="7"/>
       <c r="H137" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I137" s="1">
-        <v>2</v>
-      </c>
-      <c r="J137" s="1">
         <v>39</v>
       </c>
-      <c r="K137" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="138" spans="4:11" x14ac:dyDescent="0.65">
+    </row>
+    <row r="138" spans="4:9" x14ac:dyDescent="0.65">
       <c r="D138" t="s">
         <v>99</v>
       </c>
@@ -3507,11 +3747,11 @@
         <v>40</v>
       </c>
       <c r="G138" s="7"/>
-      <c r="J138" s="1">
+      <c r="H138" t="s">
+        <v>6</v>
+      </c>
+      <c r="I138" s="1">
         <v>40</v>
-      </c>
-      <c r="K138" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/pinout.xlsx
+++ b/documentation/pinout.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="151">
   <si>
     <t>Pin</t>
   </si>
@@ -444,6 +444,39 @@
   </si>
   <si>
     <t>DEN</t>
+  </si>
+  <si>
+    <t>SDI</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>D13</t>
   </si>
 </sst>
 </file>
@@ -1079,6 +1112,9 @@
       <c r="L9" s="1">
         <v>8</v>
       </c>
+      <c r="O9" t="s">
+        <v>142</v>
+      </c>
       <c r="P9" t="s">
         <v>97</v>
       </c>
@@ -1115,6 +1151,9 @@
       <c r="L10" s="1">
         <v>9</v>
       </c>
+      <c r="O10" t="s">
+        <v>141</v>
+      </c>
       <c r="P10" t="s">
         <v>83</v>
       </c>
@@ -1181,6 +1220,9 @@
       <c r="L12" s="1">
         <v>11</v>
       </c>
+      <c r="O12" t="s">
+        <v>144</v>
+      </c>
       <c r="P12" t="s">
         <v>96</v>
       </c>
@@ -1217,6 +1259,9 @@
       <c r="L13" s="1">
         <v>12</v>
       </c>
+      <c r="O13" t="s">
+        <v>143</v>
+      </c>
       <c r="P13" t="s">
         <v>82</v>
       </c>
@@ -1283,6 +1328,9 @@
       <c r="L15" s="1">
         <v>14</v>
       </c>
+      <c r="O15" t="s">
+        <v>146</v>
+      </c>
       <c r="P15" t="s">
         <v>95</v>
       </c>
@@ -1319,6 +1367,9 @@
       <c r="L16" s="1">
         <v>15</v>
       </c>
+      <c r="O16" t="s">
+        <v>145</v>
+      </c>
       <c r="P16" t="s">
         <v>81</v>
       </c>
@@ -1379,6 +1430,9 @@
       <c r="L18" s="1">
         <v>17</v>
       </c>
+      <c r="O18" t="s">
+        <v>148</v>
+      </c>
       <c r="P18" t="s">
         <v>94</v>
       </c>
@@ -1409,6 +1463,9 @@
       <c r="L19" s="1">
         <v>18</v>
       </c>
+      <c r="O19" t="s">
+        <v>147</v>
+      </c>
       <c r="P19" t="s">
         <v>80</v>
       </c>
@@ -1469,6 +1526,9 @@
       <c r="L21" s="1">
         <v>20</v>
       </c>
+      <c r="O21" t="s">
+        <v>150</v>
+      </c>
       <c r="P21" t="s">
         <v>93</v>
       </c>
@@ -1499,6 +1559,9 @@
       <c r="L22" s="1">
         <v>21</v>
       </c>
+      <c r="O22" t="s">
+        <v>149</v>
+      </c>
       <c r="P22" t="s">
         <v>79</v>
       </c>
@@ -1559,12 +1622,7 @@
       <c r="L24" s="1">
         <v>23</v>
       </c>
-      <c r="P24" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>19</v>
-      </c>
+      <c r="Q24" s="1"/>
       <c r="R24" s="1">
         <v>23</v>
       </c>
@@ -1589,12 +1647,7 @@
       <c r="L25" s="1">
         <v>24</v>
       </c>
-      <c r="P25" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>20</v>
-      </c>
+      <c r="Q25" s="1"/>
       <c r="R25" s="1">
         <v>24</v>
       </c>
@@ -1616,12 +1669,8 @@
       <c r="L26" s="1">
         <v>25</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>29</v>
-      </c>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="1"/>
       <c r="R26" s="1">
         <v>25</v>
       </c>
@@ -1646,12 +1695,7 @@
       <c r="L27" s="1">
         <v>26</v>
       </c>
-      <c r="P27" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q27" s="1"/>
       <c r="R27" s="1">
         <v>26</v>
       </c>
@@ -1676,12 +1720,7 @@
       <c r="L28" s="1">
         <v>27</v>
       </c>
-      <c r="P28" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>8</v>
-      </c>
+      <c r="Q28" s="1"/>
       <c r="R28" s="1">
         <v>27</v>
       </c>
@@ -2023,6 +2062,15 @@
     <row r="43" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A43" s="1"/>
       <c r="H43" s="7"/>
+      <c r="N43" t="s">
+        <v>74</v>
+      </c>
+      <c r="O43" s="1">
+        <v>37</v>
+      </c>
+      <c r="P43" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C44" s="4" t="s">
@@ -2038,6 +2086,15 @@
       <c r="L44" s="4" t="s">
         <v>0</v>
       </c>
+      <c r="N44" t="s">
+        <v>98</v>
+      </c>
+      <c r="O44" s="1">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C45" s="1">
@@ -2056,6 +2113,16 @@
         <v>1</v>
       </c>
       <c r="M45" s="7"/>
+      <c r="N45" t="s">
+        <v>84</v>
+      </c>
+      <c r="O45" s="1">
+        <v>39</v>
+      </c>
+      <c r="P45" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="7"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C46" s="1">
@@ -2081,6 +2148,16 @@
         <v>2</v>
       </c>
       <c r="M46" s="7"/>
+      <c r="N46" t="s">
+        <v>99</v>
+      </c>
+      <c r="O46" s="1">
+        <v>40</v>
+      </c>
+      <c r="P46" t="s">
+        <v>21</v>
+      </c>
+      <c r="S46" s="7"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C47" s="1">
@@ -2106,6 +2183,7 @@
         <v>3</v>
       </c>
       <c r="M47" s="7"/>
+      <c r="S47" s="7"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.65">
       <c r="C48" s="1">
@@ -2125,6 +2203,7 @@
         <v>4</v>
       </c>
       <c r="M48" s="7"/>
+      <c r="S48" s="7"/>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.65">
       <c r="C49" s="1">

--- a/documentation/pinout.xlsx
+++ b/documentation/pinout.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="150">
   <si>
     <t>Pin</t>
   </si>
@@ -339,9 +339,6 @@
   </si>
   <si>
     <t>3V3</t>
-  </si>
-  <si>
-    <t>DLDO2 camera 15</t>
   </si>
   <si>
     <t>D0N</t>
@@ -921,7 +918,7 @@
         <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I3">
         <v>38</v>
@@ -950,13 +947,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I4">
         <v>39</v>
@@ -1007,13 +1004,10 @@
         <v>82</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6">
+        <v>108</v>
+      </c>
+      <c r="I6">
         <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>105</v>
       </c>
       <c r="K6" t="s">
         <v>9</v>
@@ -1045,7 +1039,7 @@
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>10</v>
@@ -1101,7 +1095,7 @@
         <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I9">
         <v>3</v>
@@ -1113,7 +1107,7 @@
         <v>8</v>
       </c>
       <c r="O9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P9" t="s">
         <v>97</v>
@@ -1139,7 +1133,7 @@
         <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10">
@@ -1152,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P10" t="s">
         <v>83</v>
@@ -1208,7 +1202,7 @@
         <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12">
@@ -1221,7 +1215,7 @@
         <v>11</v>
       </c>
       <c r="O12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P12" t="s">
         <v>96</v>
@@ -1247,7 +1241,7 @@
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13">
@@ -1260,7 +1254,7 @@
         <v>12</v>
       </c>
       <c r="O13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P13" t="s">
         <v>82</v>
@@ -1316,7 +1310,7 @@
         <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15">
@@ -1329,7 +1323,7 @@
         <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P15" t="s">
         <v>95</v>
@@ -1355,7 +1349,7 @@
         <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16">
@@ -1368,7 +1362,7 @@
         <v>15</v>
       </c>
       <c r="O16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P16" t="s">
         <v>81</v>
@@ -1431,7 +1425,7 @@
         <v>17</v>
       </c>
       <c r="O18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P18" t="s">
         <v>94</v>
@@ -1464,7 +1458,7 @@
         <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P19" t="s">
         <v>80</v>
@@ -1527,7 +1521,7 @@
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P21" t="s">
         <v>93</v>
@@ -1560,7 +1554,7 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P22" t="s">
         <v>79</v>
@@ -1639,7 +1633,7 @@
       </c>
       <c r="H25" s="7"/>
       <c r="I25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
@@ -1687,7 +1681,7 @@
       </c>
       <c r="H27" s="7"/>
       <c r="I27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -1712,7 +1706,7 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K28" t="s">
         <v>22</v>
@@ -2081,7 +2075,7 @@
       </c>
       <c r="H44" s="11"/>
       <c r="K44" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>0</v>
@@ -2093,7 +2087,7 @@
         <v>38</v>
       </c>
       <c r="P44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.65">
@@ -2135,7 +2129,7 @@
         <v>83</v>
       </c>
       <c r="F46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H46" s="12">
         <v>35</v>
@@ -2164,13 +2158,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E47" t="s">
         <v>97</v>
       </c>
       <c r="F47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H47" s="12">
         <v>37</v>
@@ -2216,7 +2210,7 @@
         <v>82</v>
       </c>
       <c r="F49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H49" s="12"/>
       <c r="J49" s="7"/>
@@ -2239,7 +2233,7 @@
         <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H50" s="12"/>
       <c r="J50" s="7"/>
@@ -2281,14 +2275,14 @@
         <v>81</v>
       </c>
       <c r="F52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H52" s="12"/>
       <c r="J52" t="s">
         <v>53</v>
       </c>
       <c r="K52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L52" s="1">
         <v>8</v>
@@ -2306,14 +2300,14 @@
         <v>95</v>
       </c>
       <c r="F53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H53" s="12"/>
       <c r="J53" t="s">
         <v>56</v>
       </c>
       <c r="K53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L53" s="1">
         <v>9</v>
@@ -2332,7 +2326,7 @@
         <v>58</v>
       </c>
       <c r="K54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L54" s="1">
         <v>10</v>
@@ -2350,14 +2344,14 @@
         <v>80</v>
       </c>
       <c r="F55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H55" s="12"/>
       <c r="J55" t="s">
         <v>89</v>
       </c>
       <c r="K55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L55" s="1">
         <v>11</v>
@@ -2375,14 +2369,14 @@
         <v>94</v>
       </c>
       <c r="F56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H56" s="12"/>
       <c r="J56" t="s">
         <v>75</v>
       </c>
       <c r="K56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L56" s="1">
         <v>12</v>
@@ -2419,7 +2413,7 @@
         <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H58" s="12"/>
       <c r="J58" s="2" t="s">
@@ -2444,7 +2438,7 @@
         <v>93</v>
       </c>
       <c r="F59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H59" s="12">
         <v>11</v>
@@ -2453,7 +2447,7 @@
         <v>80</v>
       </c>
       <c r="K59" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L59" s="1">
         <v>15</v>
@@ -2474,7 +2468,7 @@
         <v>94</v>
       </c>
       <c r="K60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L60" s="1">
         <v>16</v>
@@ -2495,7 +2489,7 @@
         <v>79</v>
       </c>
       <c r="K61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L61" s="1">
         <v>17</v>
@@ -2516,7 +2510,7 @@
         <v>93</v>
       </c>
       <c r="K62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L62" s="1">
         <v>18</v>
@@ -2535,7 +2529,7 @@
         <v>52</v>
       </c>
       <c r="K63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L63" s="1">
         <v>19</v>
@@ -2554,7 +2548,7 @@
         <v>49</v>
       </c>
       <c r="K64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L64" s="1">
         <v>20</v>
@@ -2634,7 +2628,7 @@
         <v>97</v>
       </c>
       <c r="K68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L68" s="1">
         <v>24</v>
@@ -2655,7 +2649,7 @@
         <v>82</v>
       </c>
       <c r="K69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L69" s="1">
         <v>25</v>
@@ -2676,7 +2670,7 @@
         <v>96</v>
       </c>
       <c r="K70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L70" s="1">
         <v>26</v>
@@ -2697,7 +2691,7 @@
         <v>81</v>
       </c>
       <c r="K71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L71" s="1">
         <v>27</v>
@@ -2718,7 +2712,7 @@
         <v>95</v>
       </c>
       <c r="K72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L72" s="1">
         <v>28</v>
@@ -2756,7 +2750,7 @@
         <v>78</v>
       </c>
       <c r="K74" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L74" s="1">
         <v>30</v>
@@ -2794,7 +2788,7 @@
         <v>92</v>
       </c>
       <c r="K76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L76" s="1">
         <v>32</v>
@@ -2814,7 +2808,7 @@
         <v>91</v>
       </c>
       <c r="K77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L77" s="1">
         <v>33</v>
@@ -2834,7 +2828,7 @@
         <v>77</v>
       </c>
       <c r="K78" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L78" s="1">
         <v>34</v>
@@ -3005,7 +2999,7 @@
         <v>66</v>
       </c>
       <c r="E88" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H88" s="7"/>
     </row>
@@ -3023,7 +3017,7 @@
         <v>67</v>
       </c>
       <c r="E89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H89" s="7"/>
     </row>
@@ -3041,7 +3035,7 @@
         <v>68</v>
       </c>
       <c r="E90" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H90" s="7"/>
     </row>
@@ -3075,18 +3069,18 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.65">
       <c r="C93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.65">
       <c r="C94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.65">
@@ -3108,7 +3102,7 @@
         <v>103</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>0</v>
@@ -3269,7 +3263,7 @@
       </c>
       <c r="G106" s="7"/>
       <c r="H106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I106" s="1">
         <v>8</v>
@@ -3290,7 +3284,7 @@
       </c>
       <c r="G107" s="7"/>
       <c r="H107" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I107" s="1">
         <v>9</v>
@@ -3311,7 +3305,7 @@
       </c>
       <c r="G108" s="7"/>
       <c r="H108" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I108" s="1">
         <v>10</v>
@@ -3332,7 +3326,7 @@
       </c>
       <c r="G109" s="7"/>
       <c r="H109" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I109" s="1">
         <v>11</v>
@@ -3353,7 +3347,7 @@
       </c>
       <c r="G110" s="7"/>
       <c r="H110" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I110" s="1">
         <v>12</v>
@@ -3416,7 +3410,7 @@
       </c>
       <c r="G113" s="7"/>
       <c r="H113" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I113" s="1">
         <v>15</v>
@@ -3437,7 +3431,7 @@
       </c>
       <c r="G114" s="7"/>
       <c r="H114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I114" s="1">
         <v>16</v>
@@ -3458,7 +3452,7 @@
       </c>
       <c r="G115" s="7"/>
       <c r="H115" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I115" s="1">
         <v>17</v>
@@ -3479,7 +3473,7 @@
       </c>
       <c r="G116" s="7"/>
       <c r="H116" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I116" s="1">
         <v>18</v>
@@ -3500,7 +3494,7 @@
       </c>
       <c r="G117" s="7"/>
       <c r="H117" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I117" s="1">
         <v>19</v>
@@ -3521,7 +3515,7 @@
       </c>
       <c r="G118" s="7"/>
       <c r="H118" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I118" s="1">
         <v>20</v>
@@ -3587,7 +3581,7 @@
       </c>
       <c r="G122" s="7"/>
       <c r="H122" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I122" s="1">
         <v>24</v>
@@ -3602,7 +3596,7 @@
       </c>
       <c r="G123" s="7"/>
       <c r="H123" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I123" s="1">
         <v>25</v>
@@ -3617,7 +3611,7 @@
       </c>
       <c r="G124" s="7"/>
       <c r="H124" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I124" s="1">
         <v>26</v>
@@ -3632,7 +3626,7 @@
       </c>
       <c r="G125" s="7"/>
       <c r="H125" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I125" s="1">
         <v>27</v>
@@ -3647,7 +3641,7 @@
       </c>
       <c r="G126" s="7"/>
       <c r="H126" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I126" s="1">
         <v>28</v>
@@ -3677,7 +3671,7 @@
       </c>
       <c r="G128" s="7"/>
       <c r="H128" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I128" s="1">
         <v>30</v>
@@ -3707,7 +3701,7 @@
       </c>
       <c r="G130" s="7"/>
       <c r="H130" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I130" s="1">
         <v>32</v>
@@ -3722,7 +3716,7 @@
       </c>
       <c r="G131" s="7"/>
       <c r="H131" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I131" s="1">
         <v>33</v>
@@ -3737,7 +3731,7 @@
       </c>
       <c r="G132" s="7"/>
       <c r="H132" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I132" s="1">
         <v>34</v>
